--- a/Trail_Bish_Dynasty_Premium.xlsx
+++ b/Trail_Bish_Dynasty_Premium.xlsx
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Amari Cooper</t>
+          <t>Roquan Smith</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>ILB</t>
         </is>
       </c>
       <c r="D28" s="26" t="inlineStr">
@@ -2177,11 +2177,11 @@
         </is>
       </c>
       <c r="E28" s="16" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>Multiple Pro Bowl receiver with seven 1,000-yard receiving seasons.</t>
+          <t>Multiple All-Pro linebacker and one of the NFL's leading tacklers.</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>Laremy Tunsil</t>
+          <t>Amari Cooper</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H29" s="25" t="inlineStr">
         <is>
-          <t>Multiple All-Pro and Pro Bowl offensive tackle; among the league's premier pass protectors.</t>
+          <t>Multiple Pro Bowl receiver with seven 1,000-yard receiving seasons.</t>
         </is>
       </c>
     </row>
@@ -2239,21 +2239,21 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Allen</t>
+          <t>Laremy Tunsil</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>Matt</t>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="E30" s="16" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>Multiple Pro Bowl defensive lineman and key contributor on playoff teams.</t>
+          <t>Multiple All-Pro and Pro Bowl offensive tackle; among the league's premier pass protectors.</t>
         </is>
       </c>
     </row>
@@ -2277,17 +2277,17 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>Leonard Fournette</t>
+          <t>Jonathan Allen</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>Ryan</t>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>Matt</t>
         </is>
       </c>
       <c r="E31" s="22" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F31" s="27" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="G31" s="27" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>Pro Bowl running back and Super Bowl champion with multiple 1,000-yard seasons.</t>
+          <t>Multiple Pro Bowl defensive lineman and key contributor on playoff teams.</t>
         </is>
       </c>
     </row>
@@ -2315,12 +2315,12 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Jalen Carter</t>
+          <t>Leonard Fournette</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D32" s="26" t="inlineStr">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="E32" s="16" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="H32" s="19" t="inlineStr">
         <is>
-          <t>Pro Bowl defensive tackle and key contributor on elite defenses.</t>
+          <t>Pro Bowl running back and Super Bowl champion with multiple 1,000-yard seasons.</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>Roquan Smith</t>
+          <t>Jalen Carter</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>ILB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -2367,11 +2367,11 @@
         </is>
       </c>
       <c r="E33" s="22" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="F33" s="27" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="G33" s="27" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="H33" s="25" t="inlineStr">
         <is>
-          <t>Multiple All-Pro linebacker and one of the NFL's leading tacklers.</t>
+          <t>Pro Bowl defensive tackle and key contributor on elite defenses.</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14696,7 @@
       </c>
       <c r="D5" s="37" t="inlineStr">
         <is>
-          <t>59.97</t>
+          <t>59.98</t>
         </is>
       </c>
       <c r="E5" s="37" t="inlineStr">

--- a/Trail_Bish_Dynasty_Premium.xlsx
+++ b/Trail_Bish_Dynasty_Premium.xlsx
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="C115" s="22" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D115" s="27" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="C236" s="16" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D236" s="26" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="C263" s="22" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D263" s="23" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="C280" s="16" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D280" s="17" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="C299" s="22" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D299" s="27" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="C343" s="22" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="D343" s="27" t="inlineStr">
